--- a/项目进度表.xlsx
+++ b/项目进度表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dogs\Desktop\基于FOC的二阶倒立摆系统\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dogs\Desktop\MotorCtrl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D79BBC0-2CAD-411C-80E3-ED08D7DCD6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F02DD4D-3035-41D1-B597-B27799B8266A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{2A991C1C-22C3-45A1-9608-BFC91CEB4541}"/>
   </bookViews>
@@ -20,12 +20,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>完成20%时间点</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -72,10 +81,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>项目板块划分3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>完成成果文件路径（包含文件名）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -84,35 +89,94 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>电源转换电路</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>电机驱动电路</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>MCU最小系统</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>烧录电路</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝牙串口通信电路</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>三相逆变器（6MOS）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>电流采样方案</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>设计参考来源</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>电机驱动</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>栅极驱动电路</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>烧录接口</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>三相逆变桥</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>电流采样电路</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋转电位器调速接口</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>串口通信调试接口</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>编码器接口</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>防反接设计是重点，需要我们搜集优秀电路，
+写方案决定用哪一个，考虑成本和性能平衡
+（Alt+Enter同一单元格换行）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>电源转换电路（输入是12V）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU型号暂定为：STM32G473CBT6
+画原理图请注意解耦，以便后续替换MCU型号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>待定，先别管</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6个NMOS搭建</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>采取两电阻在相采样方案</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ST-Link</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>用于与上位机通信，调试</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>型号选型类似</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">芯片选型：MT6701, 通信协议SPI </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 注意：注意测试点端口，LED灯提示， 还需要3颗左右的LED灯</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -120,7 +184,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,8 +224,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -184,6 +256,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -194,7 +271,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -204,30 +281,40 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="差" xfId="1" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="3" builtinId="26"/>
     <cellStyle name="适中" xfId="2" builtinId="28"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -540,179 +627,234 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8519356F-2E36-4CE4-A5FC-9C5A819ED847}">
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="4" width="41.08203125" customWidth="1"/>
-    <col min="5" max="5" width="18.9140625" customWidth="1"/>
-    <col min="6" max="6" width="14.9140625" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="33.75" customWidth="1"/>
+    <col min="1" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="5" width="41.08203125" customWidth="1"/>
+    <col min="6" max="6" width="18.9140625" customWidth="1"/>
+    <col min="7" max="7" width="14.9140625" customWidth="1"/>
+    <col min="8" max="8" width="14.1640625" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="33.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-    </row>
-    <row r="4" spans="1:23" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+    </row>
+    <row r="4" spans="1:24" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="K4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="68.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="6"/>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="6"/>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="6"/>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="6"/>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="6"/>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="6"/>
+      <c r="C12" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="S26" t="e">
-        <f>+R26:S2S25:S26</f>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="6"/>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T26" t="e">
+        <f>+S26:S2S25:T26</f>
         <v>#NAME?</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:A18"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A1:W2"/>
+    <mergeCell ref="A1:X2"/>
+    <mergeCell ref="B5:B15"/>
+    <mergeCell ref="C14:D15"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/项目进度表.xlsx
+++ b/项目进度表.xlsx
@@ -295,20 +295,20 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -727,31 +727,31 @@
       </c>
     </row>
     <row r="5" spans="1:24" ht="68.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="6"/>
       <c r="C7" t="s">
         <v>13</v>
@@ -761,7 +761,7 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
+      <c r="A8" s="4"/>
       <c r="B8" s="6"/>
       <c r="C8" t="s">
         <v>16</v>
@@ -771,7 +771,7 @@
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="6"/>
       <c r="C9" t="s">
         <v>17</v>
@@ -781,7 +781,7 @@
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="6"/>
       <c r="C10" t="s">
         <v>15</v>
@@ -791,7 +791,7 @@
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
+      <c r="A11" s="4"/>
       <c r="B11" s="6"/>
       <c r="C11" t="s">
         <v>19</v>
@@ -801,7 +801,7 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
+      <c r="A12" s="4"/>
       <c r="B12" s="6"/>
       <c r="C12" t="s">
         <v>18</v>
@@ -811,7 +811,7 @@
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
+      <c r="A13" s="4"/>
       <c r="B13" s="6"/>
       <c r="C13" t="s">
         <v>20</v>
@@ -821,27 +821,27 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
+      <c r="A14" s="4"/>
       <c r="B14" s="6"/>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="6"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
+      <c r="A16" s="4"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
+      <c r="A17" s="4"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
+      <c r="A18" s="4"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="T26" t="e">

--- a/项目进度表.xlsx
+++ b/项目进度表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dogs\Desktop\MotorCtrl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F02DD4D-3035-41D1-B597-B27799B8266A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50531D8-57DD-4F83-83A6-DD1E416D944C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{2A991C1C-22C3-45A1-9608-BFC91CEB4541}"/>
   </bookViews>
@@ -125,14 +125,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>串口通信调试接口</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>编码器接口</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>防反接设计是重点，需要我们搜集优秀电路，
 写方案决定用哪一个，考虑成本和性能平衡
 （Alt+Enter同一单元格换行）</t>
@@ -160,14 +152,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ST-Link</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>用于与上位机通信，调试</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>型号选型类似</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -177,6 +161,22 @@
   </si>
   <si>
     <t xml:space="preserve"> 注意：注意测试点端口，LED灯提示， 还需要3颗左右的LED灯</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">编码器接口 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>串口通信</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>用于与上位机通信</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ST-Link,调试仿真</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -734,10 +734,10 @@
         <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="55" customHeight="1" x14ac:dyDescent="0.3">
@@ -747,7 +747,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
@@ -757,7 +757,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -767,7 +767,7 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
@@ -777,7 +777,7 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
@@ -787,17 +787,17 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="6"/>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
@@ -807,24 +807,24 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="6"/>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D14" s="7"/>
     </row>
